--- a/ALTS_TUTORIAL1.xlsx
+++ b/ALTS_TUTORIAL1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lcim\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA6EE969-2578-4F06-935F-68BC83A66C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75EE1D08-E11B-4C72-99F7-8055084E08EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{C99A092A-B441-48D6-AE9F-9C74564E313B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
   <si>
     <t>Client</t>
   </si>
@@ -77,10 +77,25 @@
     <t>In_copy</t>
   </si>
   <si>
-    <t>ICTS</t>
-  </si>
-  <si>
-    <t>M365</t>
+    <t>AddressLine1</t>
+  </si>
+  <si>
+    <t>AddressLine2</t>
+  </si>
+  <si>
+    <t>AddressLine3</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>FDL</t>
+  </si>
+  <si>
+    <t>M365 Subscription</t>
   </si>
   <si>
     <t>Annually</t>
@@ -89,49 +104,85 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>ictsolutionsforeveryone@gmail.com</t>
+  </si>
+  <si>
+    <t>favoradi@yahoo.com;leonard.mbibi@gregobyte.com</t>
+  </si>
+  <si>
+    <t>123 Aba Owerri Road</t>
+  </si>
+  <si>
+    <t>Aba, Abia State</t>
+  </si>
+  <si>
+    <t>GTL</t>
+  </si>
+  <si>
+    <t>BitDefender Subscription</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>l.cim@outlook.com</t>
   </si>
   <si>
-    <t>favoradi@yahoo.com;leonard.mbibi@gregobyte.com</t>
-  </si>
-  <si>
-    <t>GTL</t>
-  </si>
-  <si>
-    <t>BitDefender</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>leonard.mbibi@gregobyte.com</t>
   </si>
   <si>
-    <t>FDL</t>
-  </si>
-  <si>
-    <t>Internet Service</t>
-  </si>
-  <si>
-    <t>ictsolutionsforeveryone@gmail.com</t>
+    <t>76 Ndiukwu Street</t>
+  </si>
+  <si>
+    <t>By NHS Junction, Near PADESCO, Arondizuogu</t>
+  </si>
+  <si>
+    <t>Imo State</t>
+  </si>
+  <si>
+    <t>Internet Service Subscription</t>
   </si>
   <si>
     <t>lcim1104@gmail.com</t>
   </si>
   <si>
+    <t>12 Ugbana Lane</t>
+  </si>
+  <si>
+    <t>Off Ukpor Lane</t>
+  </si>
+  <si>
+    <t>Umuoji, Anambra State</t>
+  </si>
+  <si>
     <t>GPPS</t>
   </si>
   <si>
-    <t>IT Support</t>
+    <t>IT Support Contract</t>
   </si>
   <si>
     <t>Quarterly</t>
   </si>
   <si>
+    <t>5 Amichi Crescent, Near ZOE Ministries,</t>
+  </si>
+  <si>
+    <t>Off ESBS Bust Stop</t>
+  </si>
+  <si>
+    <t>Ind. Layout, Enugu</t>
+  </si>
+  <si>
     <t>SOBAZ</t>
+  </si>
+  <si>
+    <t>102 Oderigwugwu Street, Near Nkwo Achi,</t>
+  </si>
+  <si>
+    <t>Ndiakeme, Arondizuogu</t>
   </si>
 </sst>
 </file>
@@ -142,7 +193,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -172,6 +223,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -195,7 +252,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -229,6 +286,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -237,7 +300,22 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="20">
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -274,7 +352,7 @@
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -289,8 +367,8 @@
         <color theme="0"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -301,8 +379,8 @@
         <color theme="1"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -323,16 +401,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>314325</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -355,7 +433,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10020300" y="0"/>
+          <a:off x="8343900" y="2828925"/>
           <a:ext cx="1647825" cy="704850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -369,29 +447,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CE646ED-C430-4BD8-8419-D5D2B8044C1B}" name="Table1" displayName="Table1" ref="A1:L6" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A1:L6" xr:uid="{3CE646ED-C430-4BD8-8419-D5D2B8044C1B}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{C3EC2CF2-5208-4763-8E7B-6352BBA4F583}" name="Client" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{BBFF85DA-5672-40D0-91ED-36AEE426DBB1}" name="Service" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{3A6211B1-7E6A-49CD-8AE5-BE94582514FE}" name="Cost" dataDxfId="9" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{52BDCDB7-8AB8-4548-9711-F5BBDBFACC8B}" name="Billing" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{1A409EFE-6E40-45AB-BDF1-017832EC62BE}" name="LastPaid" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{29D114DB-9AF3-4159-9962-1E46EE3073E2}" name="ActiveStatus" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{422E9FCE-0ED0-4811-89CB-34C0ED3F0BA1}" name="NextRenewal" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CE646ED-C430-4BD8-8419-D5D2B8044C1B}" name="Table1" displayName="Table1" ref="A1:Q6" totalsRowShown="0" headerRowDxfId="17">
+  <autoFilter ref="A1:Q6" xr:uid="{3CE646ED-C430-4BD8-8419-D5D2B8044C1B}"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{C3EC2CF2-5208-4763-8E7B-6352BBA4F583}" name="Client" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{BBFF85DA-5672-40D0-91ED-36AEE426DBB1}" name="Service" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{3A6211B1-7E6A-49CD-8AE5-BE94582514FE}" name="Cost" dataDxfId="14" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{52BDCDB7-8AB8-4548-9711-F5BBDBFACC8B}" name="Billing" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{1A409EFE-6E40-45AB-BDF1-017832EC62BE}" name="LastPaid" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{29D114DB-9AF3-4159-9962-1E46EE3073E2}" name="ActiveStatus" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{422E9FCE-0ED0-4811-89CB-34C0ED3F0BA1}" name="NextRenewal" dataDxfId="10">
       <calculatedColumnFormula>IF(Table1[[#This Row],[ActiveStatus]]="No", "inactive", EDATE(Table1[[#This Row],[LastPaid]], IF(Table1[[#This Row],[Billing]]="Monthly", 1, IF(Table1[[#This Row],[Billing]]="Quarterly", 3, 12))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{EDDBECA9-45F3-4603-8801-6BA309245334}" name="Alert" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{EDDBECA9-45F3-4603-8801-6BA309245334}" name="Alert" dataDxfId="9">
       <calculatedColumnFormula>IF(Table1[[#This Row],[ActiveStatus]] = "No", "Inactive", IF(Table1[[#This Row],[NextRenewal]] - TODAY() &lt;= 3, "Act now - Invoice due", IF(Table1[[#This Row],[NextRenewal]] - TODAY() &lt;= 7, "Invoice is fast approaching", "No action needed")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{48232A19-6BF8-409A-B1EF-BBBC97ACB2CB}" name="Remarks" dataDxfId="3">
+    <tableColumn id="9" xr3:uid="{48232A19-6BF8-409A-B1EF-BBBC97ACB2CB}" name="Remarks" dataDxfId="8">
       <calculatedColumnFormula>IF(Table1[[#This Row],[ActiveStatus]]  = "No", "Bill canceled", IF((Table1[[#This Row],[NextRenewal]] - TODAY()) &lt; 0, ABS(Table1[[#This Row],[NextRenewal]] - TODAY()) &amp; IF(ABS(Table1[[#This Row],[NextRenewal]] - TODAY()) = 1, " day", " days") &amp; " overdue", Table1[[#This Row],[NextRenewal]] - TODAY() &amp; IF(Table1[[#This Row],[NextRenewal]] - TODAY() = 1, " day", " days") &amp; " left"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35DD18F2-F542-4DC0-8F87-3915BF6652B6}" name="EmailDeterminant" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{35DD18F2-F542-4DC0-8F87-3915BF6652B6}" name="EmailDeterminant" dataDxfId="7">
       <calculatedColumnFormula>INT(IF(Table1[[#This Row],[ActiveStatus]] = "No", -1000, Table1[[#This Row],[NextRenewal]] - TODAY()))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6920BFC4-1208-4833-8A3B-10DC32045769}" name="Emails" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{3FA09B4F-B72C-4159-8940-D69A6F2E3C5C}" name="In_copy" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{6920BFC4-1208-4833-8A3B-10DC32045769}" name="Emails" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{3FA09B4F-B72C-4159-8940-D69A6F2E3C5C}" name="In_copy" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{07BE456D-268D-4885-BD6A-C74834D63905}" name="AddressLine1" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{A06F4AEC-DE77-4CFB-932E-B07264F9CE5C}" name="AddressLine2" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{83745DDD-CE74-439B-891B-92FD1281FDB5}" name="AddressLine3" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{3B49A428-D6B6-4433-A938-8ACFE7B879CE}" name="QTY" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{E7651678-C5C8-4DC4-9A84-7E4ECE910D1F}" name="Discount" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -714,19 +797,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E19EDBF1-18D1-4EC5-8B39-C7777102D902}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="5" width="10.125" customWidth="1"/>
+    <col min="1" max="1" width="10.125" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="3" max="5" width="10.125" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
     <col min="7" max="7" width="10.125" customWidth="1"/>
     <col min="8" max="8" width="14.375" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
     <col min="10" max="11" width="11.125" customWidth="1"/>
     <col min="12" max="12" width="15.75" customWidth="1"/>
+    <col min="13" max="13" width="16.25" customWidth="1"/>
+    <col min="14" max="14" width="15.875" customWidth="1"/>
+    <col min="15" max="15" width="16.125" customWidth="1"/>
+    <col min="17" max="17" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30.75">
+    <row r="1" spans="1:17" ht="30.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -763,29 +852,44 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" ht="46.5">
+    <row r="2" spans="1:17" ht="46.5">
       <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="C2" s="5">
         <v>1700378</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" s="6">
-        <v>45876</v>
+        <v>45879</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G2" s="6">
         <f>IF(Table1[[#This Row],[ActiveStatus]]="No", "inactive", EDATE(Table1[[#This Row],[LastPaid]], IF(Table1[[#This Row],[Billing]]="Monthly", 1, IF(Table1[[#This Row],[Billing]]="Quarterly", 3, 12))))</f>
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="H2" s="7" t="str">
         <f ca="1">IF(Table1[[#This Row],[ActiveStatus]] = "No", "Inactive", IF(Table1[[#This Row],[NextRenewal]] - TODAY() &lt;= 3, "Act now - Invoice due", IF(Table1[[#This Row],[NextRenewal]] - TODAY() &lt;= 7, "Invoice is fast approaching", "No action needed")))</f>
@@ -793,37 +897,50 @@
       </c>
       <c r="I2" s="4" t="str">
         <f ca="1">IF(Table1[[#This Row],[ActiveStatus]]  = "No", "Bill canceled", IF((Table1[[#This Row],[NextRenewal]] - TODAY()) &lt; 0, ABS(Table1[[#This Row],[NextRenewal]] - TODAY()) &amp; IF(ABS(Table1[[#This Row],[NextRenewal]] - TODAY()) = 1, " day", " days") &amp; " overdue", Table1[[#This Row],[NextRenewal]] - TODAY() &amp; IF(Table1[[#This Row],[NextRenewal]] - TODAY() = 1, " day", " days") &amp; " left"))</f>
-        <v>0 days left</v>
+        <v>5 days overdue</v>
       </c>
       <c r="J2" s="10">
         <f ca="1">INT(IF(Table1[[#This Row],[ActiveStatus]] = "No", -1000, Table1[[#This Row],[NextRenewal]] - TODAY()))</f>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="13">
+        <v>100000</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="46.5">
+    <row r="3" spans="1:17" ht="30.75">
       <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C3" s="5">
         <v>128500</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E3" s="6">
         <v>46188</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G3" s="6" t="str">
         <f>IF(Table1[[#This Row],[ActiveStatus]]="No", "inactive", EDATE(Table1[[#This Row],[LastPaid]], IF(Table1[[#This Row],[Billing]]="Monthly", 1, IF(Table1[[#This Row],[Billing]]="Quarterly", 3, 12))))</f>
@@ -842,35 +959,47 @@
         <v>-1000</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="11"/>
+        <v>30</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="30.75">
+    <row r="4" spans="1:17" ht="46.5">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C4" s="5">
         <v>50000</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46216</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="6">
-        <v>46208</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="G4" s="6">
         <f>IF(Table1[[#This Row],[ActiveStatus]]="No", "inactive", EDATE(Table1[[#This Row],[LastPaid]], IF(Table1[[#This Row],[Billing]]="Monthly", 1, IF(Table1[[#This Row],[Billing]]="Quarterly", 3, 12))))</f>
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="H4" s="7" t="str">
         <f ca="1">IF(Table1[[#This Row],[ActiveStatus]] = "No", "Inactive", IF(Table1[[#This Row],[NextRenewal]] - TODAY() &lt;= 3, "Act now - Invoice due", IF(Table1[[#This Row],[NextRenewal]] - TODAY() &lt;= 7, "Invoice is fast approaching", "No action needed")))</f>
@@ -885,30 +1014,43 @@
         <v>-2</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>26</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:13" ht="45">
+    <row r="5" spans="1:17" ht="30.75">
       <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="C5" s="5">
         <v>2000000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E5" s="6">
         <v>46254</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G5" s="6">
         <f>IF(Table1[[#This Row],[ActiveStatus]]="No", "inactive", EDATE(Table1[[#This Row],[LastPaid]], IF(Table1[[#This Row],[Billing]]="Monthly", 1, IF(Table1[[#This Row],[Billing]]="Quarterly", 3, 12))))</f>
@@ -920,37 +1062,52 @@
       </c>
       <c r="I5" s="4" t="str">
         <f ca="1">IF(Table1[[#This Row],[ActiveStatus]]  = "No", "Bill canceled", IF((Table1[[#This Row],[NextRenewal]] - TODAY()) &lt; 0, ABS(Table1[[#This Row],[NextRenewal]] - TODAY()) &amp; IF(ABS(Table1[[#This Row],[NextRenewal]] - TODAY()) = 1, " day", " days") &amp; " overdue", Table1[[#This Row],[NextRenewal]] - TODAY() &amp; IF(Table1[[#This Row],[NextRenewal]] - TODAY() = 1, " day", " days") &amp; " left"))</f>
-        <v>105 days left</v>
+        <v>97 days left</v>
       </c>
       <c r="J5" s="10">
         <f ca="1">INT(IF(Table1[[#This Row],[ActiveStatus]] = "No", -1000, Table1[[#This Row],[NextRenewal]] - TODAY()))</f>
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>54000</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="30.75">
+    <row r="6" spans="1:17" ht="30.75">
       <c r="A6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="C6" s="5">
         <v>2555000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6" s="12">
         <v>45748</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G6" s="6">
         <f>IF(Table1[[#This Row],[ActiveStatus]]="No", "inactive", EDATE(Table1[[#This Row],[LastPaid]], IF(Table1[[#This Row],[Billing]]="Monthly", 1, IF(Table1[[#This Row],[Billing]]="Quarterly", 3, 12))))</f>
@@ -962,25 +1119,42 @@
       </c>
       <c r="I6" s="4" t="str">
         <f ca="1">IF(Table1[[#This Row],[ActiveStatus]]  = "No", "Bill canceled", IF((Table1[[#This Row],[NextRenewal]] - TODAY()) &lt; 0, ABS(Table1[[#This Row],[NextRenewal]] - TODAY()) &amp; IF(ABS(Table1[[#This Row],[NextRenewal]] - TODAY()) = 1, " day", " days") &amp; " overdue", Table1[[#This Row],[NextRenewal]] - TODAY() &amp; IF(Table1[[#This Row],[NextRenewal]] - TODAY() = 1, " day", " days") &amp; " left"))</f>
-        <v>128 days overdue</v>
+        <v>136 days overdue</v>
       </c>
       <c r="J6" s="10">
         <f ca="1">INT(IF(Table1[[#This Row],[ActiveStatus]] = "No", -1000, Table1[[#This Row],[NextRenewal]] - TODAY()))</f>
-        <v>-128</v>
+        <v>-136</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" spans="1:17" ht="15.75"/>
+    <row r="8" spans="1:17" ht="18.75">
+      <c r="H8" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>AND(J2 &gt;= 0, J2 &lt;= 3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>J2 &lt; 0</formula>
     </cfRule>
   </conditionalFormatting>
